--- a/laporan_padel_dki_jakarta_2026-10-28.xlsx
+++ b/laporan_padel_dki_jakarta_2026-10-28.xlsx
@@ -699,16 +699,16 @@
         <v>68</v>
       </c>
       <c r="D9" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>38.2%</t>
+          <t>41.2%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rp2.574.000</t>
+          <t>Rp2.772.000</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1133,16 +1133,16 @@
         <v>102</v>
       </c>
       <c r="D23" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>24.5%</t>
+          <t>25.5%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp4.650.000</t>
+          <t>Rp4.800.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1195,16 +1195,16 @@
         <v>64</v>
       </c>
       <c r="D25" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>17.2%</t>
+          <t>18.8%</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rp2.600.000</t>
+          <t>Rp2.725.000</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1226,16 +1226,16 @@
         <v>68</v>
       </c>
       <c r="D26" t="n">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>16.2%</t>
+          <t>7.4%</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rp1.465.000</t>
+          <t>Rp925.000</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1598,16 +1598,16 @@
         <v>64</v>
       </c>
       <c r="D38" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>40.6%</t>
+          <t>43.8%</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rp5.380.000</t>
+          <t>Rp5.720.000</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -1970,16 +1970,16 @@
         <v>26</v>
       </c>
       <c r="D50" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>3.8%</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp115.000</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -2280,16 +2280,16 @@
         <v>36</v>
       </c>
       <c r="D60" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>5.6%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Rp298.000</t>
+          <t>Rp496.000</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -2311,16 +2311,16 @@
         <v>80</v>
       </c>
       <c r="D61" t="n">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>7.5%</t>
+          <t>5.0%</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Rp960.000</t>
+          <t>Rp720.000</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -2373,16 +2373,16 @@
         <v>72</v>
       </c>
       <c r="D63" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>23.6%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Rp2.470.000</t>
+          <t>Rp2.560.000</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -2621,16 +2621,16 @@
         <v>108</v>
       </c>
       <c r="D71" t="n">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>35.2%</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Rp7.005.500</t>
+          <t>Rp7.203.500</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -2683,16 +2683,16 @@
         <v>72</v>
       </c>
       <c r="D73" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>13.9%</t>
+          <t>15.3%</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Rp1.415.000</t>
+          <t>Rp1.490.000</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -3086,16 +3086,16 @@
         <v>102</v>
       </c>
       <c r="D86" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>22.5%</t>
+          <t>23.5%</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Rp5.100.000</t>
+          <t>Rp5.250.000</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -3912,16 +3912,16 @@
         <v>144</v>
       </c>
       <c r="D10" t="n">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>8.3%</t>
+          <t>9.0%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp1.948.000</t>
+          <t>Rp2.123.000</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4036,16 +4036,16 @@
         <v>70</v>
       </c>
       <c r="D14" t="n">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>24.3%</t>
+          <t>28.6%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp1.700.000</t>
+          <t>Rp2.000.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -4067,16 +4067,16 @@
         <v>48</v>
       </c>
       <c r="D15" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>31.2%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rp3.200.000</t>
+          <t>Rp3.480.000</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -4408,16 +4408,16 @@
         <v>17</v>
       </c>
       <c r="D26" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>5.9%</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp75.000</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -4842,16 +4842,16 @@
         <v>54</v>
       </c>
       <c r="D40" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>7.4%</t>
+          <t>9.3%</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rp800.000</t>
+          <t>Rp925.000</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -5214,16 +5214,16 @@
         <v>54</v>
       </c>
       <c r="D52" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>48.1%</t>
+          <t>51.9%</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Rp6.400.000</t>
+          <t>Rp7.200.000</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -5335,14 +5335,14 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>80</v>
+        <v>106</v>
       </c>
       <c r="D56" t="n">
-        <v>67</v>
+        <v>93</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>16.2%</t>
+          <t>12.3%</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -5369,16 +5369,16 @@
         <v>75</v>
       </c>
       <c r="D57" t="n">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>4.0%</t>
+          <t>6.7%</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Rp213.000</t>
+          <t>Rp337.000</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -6133,16 +6133,16 @@
         <v>256</v>
       </c>
       <c r="D8" t="n">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>23.8%</t>
+          <t>24.2%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rp29.850.000</t>
+          <t>Rp30.100.000</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -6226,16 +6226,16 @@
         <v>72</v>
       </c>
       <c r="D11" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>27.8%</t>
+          <t>30.6%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rp5.200.000</t>
+          <t>Rp5.560.000</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -6412,16 +6412,16 @@
         <v>102</v>
       </c>
       <c r="D17" t="n">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>14.7%</t>
+          <t>18.6%</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rp6.600.000</t>
+          <t>Rp7.975.000</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -6474,16 +6474,16 @@
         <v>48</v>
       </c>
       <c r="D19" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>20.8%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rp1.750.000</t>
+          <t>Rp2.150.000</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -6505,16 +6505,16 @@
         <v>15</v>
       </c>
       <c r="D20" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>13.3%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rp456.000</t>
+          <t>Rp684.000</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -6711,16 +6711,16 @@
         <v>90</v>
       </c>
       <c r="D5" t="n">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>4.4%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp337.000</t>
+          <t>Rp406.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -6742,16 +6742,16 @@
         <v>216</v>
       </c>
       <c r="D6" t="n">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>21.3%</t>
+          <t>23.6%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rp10.020.000</t>
+          <t>Rp10.935.000</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -6990,16 +6990,16 @@
         <v>72</v>
       </c>
       <c r="D14" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>30.6%</t>
+          <t>31.9%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp5.570.000</t>
+          <t>Rp5.845.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -7083,16 +7083,16 @@
         <v>144</v>
       </c>
       <c r="D17" t="n">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>14.6%</t>
+          <t>16.0%</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rp4.800.000</t>
+          <t>Rp5.000.000</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7269,16 +7269,16 @@
         <v>126</v>
       </c>
       <c r="D23" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>34.9%</t>
+          <t>34.1%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp6.166.000</t>
+          <t>Rp6.041.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -7300,16 +7300,16 @@
         <v>90</v>
       </c>
       <c r="D24" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>26.7%</t>
+          <t>28.9%</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rp5.595.000</t>
+          <t>Rp5.895.000</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -7579,16 +7579,16 @@
         <v>72</v>
       </c>
       <c r="D33" t="n">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rp3.100.000</t>
+          <t>Rp1.960.000</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -7641,16 +7641,16 @@
         <v>187</v>
       </c>
       <c r="D35" t="n">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>39.0%</t>
+          <t>39.6%</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rp14.025.000</t>
+          <t>Rp14.075.000</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -7734,16 +7734,16 @@
         <v>170</v>
       </c>
       <c r="D38" t="n">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>17.1%</t>
+          <t>18.2%</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rp3.750.000</t>
+          <t>Rp4.150.000</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -7827,16 +7827,16 @@
         <v>150</v>
       </c>
       <c r="D41" t="n">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>52.7%</t>
+          <t>54.0%</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rp24.350.000</t>
+          <t>Rp25.050.000</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -7858,16 +7858,16 @@
         <v>120</v>
       </c>
       <c r="D42" t="n">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>7.5%</t>
+          <t>5.8%</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rp4.197.000</t>
+          <t>Rp3.397.000</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -8312,16 +8312,16 @@
         <v>136</v>
       </c>
       <c r="D3" t="n">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>31.6%</t>
+          <t>32.4%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp7.955.000</t>
+          <t>Rp8.055.000</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -8405,16 +8405,16 @@
         <v>72</v>
       </c>
       <c r="D6" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>19.4%</t>
+          <t>20.8%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rp3.886.000</t>
+          <t>Rp4.061.000</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -8591,16 +8591,16 @@
         <v>26</v>
       </c>
       <c r="D12" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>30.8%</t>
+          <t>23.1%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rp792.000</t>
+          <t>Rp594.000</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -8622,16 +8622,16 @@
         <v>51</v>
       </c>
       <c r="D13" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>37.3%</t>
+          <t>41.2%</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rp2.974.992</t>
+          <t>Rp3.224.992</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -8653,16 +8653,16 @@
         <v>72</v>
       </c>
       <c r="D14" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>8.3%</t>
+          <t>9.7%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp750.000</t>
+          <t>Rp875.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -8808,16 +8808,16 @@
         <v>102</v>
       </c>
       <c r="D19" t="n">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>63.7%</t>
+          <t>68.6%</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rp24.120.000</t>
+          <t>Rp26.080.000</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8901,16 +8901,16 @@
         <v>144</v>
       </c>
       <c r="D22" t="n">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>13.2%</t>
+          <t>13.9%</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rp3.660.000</t>
+          <t>Rp3.840.000</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -8932,16 +8932,16 @@
         <v>36</v>
       </c>
       <c r="D23" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>30.6%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp1.756.000</t>
+          <t>Rp1.891.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -9056,16 +9056,16 @@
         <v>32</v>
       </c>
       <c r="D27" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>21.9%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rp1.015.000</t>
+          <t>Rp1.140.000</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -9118,16 +9118,16 @@
         <v>32</v>
       </c>
       <c r="D29" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>31.2%</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rp2.200.000</t>
+          <t>Rp1.450.000</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -9242,16 +9242,16 @@
         <v>36</v>
       </c>
       <c r="D33" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>19.4%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rp1.480.000</t>
+          <t>Rp1.580.000</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -9335,16 +9335,16 @@
         <v>72</v>
       </c>
       <c r="D36" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>27.8%</t>
+          <t>30.6%</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rp1.882.000</t>
+          <t>Rp2.080.000</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -9375,7 +9375,7 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rp3.810.000</t>
+          <t>Rp3.740.000</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -9397,16 +9397,16 @@
         <v>64</v>
       </c>
       <c r="D38" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>6.2%</t>
+          <t>7.8%</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rp588.000</t>
+          <t>Rp713.000</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -9428,16 +9428,16 @@
         <v>90</v>
       </c>
       <c r="D39" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>10.0%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rp2.100.000</t>
+          <t>Rp2.275.000</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">

--- a/laporan_padel_dki_jakarta_2026-10-28.xlsx
+++ b/laporan_padel_dki_jakarta_2026-10-28.xlsx
@@ -544,16 +544,16 @@
         <v>144</v>
       </c>
       <c r="D4" t="n">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>17.4%</t>
+          <t>18.8%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rp12.030.000</t>
+          <t>Rp12.460.000</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -575,16 +575,16 @@
         <v>80</v>
       </c>
       <c r="D5" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>13.8%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp1.092.000</t>
+          <t>Rp1.191.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -637,16 +637,16 @@
         <v>64</v>
       </c>
       <c r="D7" t="n">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>9.4%</t>
+          <t>18.8%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rp716.000</t>
+          <t>Rp1.526.000</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -761,16 +761,16 @@
         <v>126</v>
       </c>
       <c r="D11" t="n">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>8.7%</t>
+          <t>9.5%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rp3.125.000</t>
+          <t>Rp3.375.000</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -792,16 +792,16 @@
         <v>96</v>
       </c>
       <c r="D12" t="n">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>19.8%</t>
+          <t>21.9%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rp5.730.000</t>
+          <t>Rp6.120.000</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1133,16 +1133,16 @@
         <v>102</v>
       </c>
       <c r="D23" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>25.5%</t>
+          <t>26.5%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp4.800.000</t>
+          <t>Rp5.000.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1195,16 +1195,16 @@
         <v>64</v>
       </c>
       <c r="D25" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>18.8%</t>
+          <t>20.3%</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rp2.725.000</t>
+          <t>Rp2.850.000</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1319,16 +1319,16 @@
         <v>16</v>
       </c>
       <c r="D29" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>6.2%</t>
+          <t>18.8%</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rp125.000</t>
+          <t>Rp501.000</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -1505,16 +1505,16 @@
         <v>72</v>
       </c>
       <c r="D35" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>19.4%</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rp1.716.000</t>
+          <t>Rp1.982.000</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -1567,16 +1567,16 @@
         <v>72</v>
       </c>
       <c r="D37" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>43.1%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rp4.785.000</t>
+          <t>Rp4.975.000</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -1753,16 +1753,16 @@
         <v>234</v>
       </c>
       <c r="D43" t="n">
-        <v>220</v>
+        <v>214</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>6.0%</t>
+          <t>8.5%</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rp2.692.000</t>
+          <t>Rp4.792.000</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -1939,16 +1939,16 @@
         <v>105</v>
       </c>
       <c r="D49" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>28.6%</t>
+          <t>29.5%</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Rp5.900.000</t>
+          <t>Rp6.050.000</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -2032,16 +2032,16 @@
         <v>64</v>
       </c>
       <c r="D52" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>18.8%</t>
+          <t>21.9%</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Rp3.456.000</t>
+          <t>Rp4.032.000</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -2249,16 +2249,16 @@
         <v>32</v>
       </c>
       <c r="D59" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>28.1%</t>
+          <t>31.2%</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Rp2.075.000</t>
+          <t>Rp2.300.000</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -2418,7 +2418,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Rp70.000 - Rp99.000</t>
+          <t>Rp75.000 - Rp99.000</t>
         </is>
       </c>
     </row>
@@ -2528,16 +2528,16 @@
         <v>41</v>
       </c>
       <c r="D68" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>2.4%</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp230.000</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -2683,16 +2683,16 @@
         <v>72</v>
       </c>
       <c r="D73" t="n">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>15.3%</t>
+          <t>9.7%</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Rp1.490.000</t>
+          <t>Rp810.000</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -2776,16 +2776,16 @@
         <v>98</v>
       </c>
       <c r="D76" t="n">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>3.1%</t>
+          <t>4.1%</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Rp750.000</t>
+          <t>Rp900.000</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -2807,16 +2807,16 @@
         <v>45</v>
       </c>
       <c r="D77" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>31.1%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Rp2.100.000</t>
+          <t>Rp2.250.000</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -2900,16 +2900,16 @@
         <v>114</v>
       </c>
       <c r="D80" t="n">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>4.4%</t>
+          <t>2.6%</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Rp1.850.000</t>
+          <t>Rp850.000</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -2931,16 +2931,16 @@
         <v>126</v>
       </c>
       <c r="D81" t="n">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>25.4%</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Rp3.572.000</t>
+          <t>Rp4.368.000</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -3086,16 +3086,16 @@
         <v>102</v>
       </c>
       <c r="D86" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>23.5%</t>
+          <t>24.5%</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Rp5.250.000</t>
+          <t>Rp5.550.000</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -3117,16 +3117,16 @@
         <v>36</v>
       </c>
       <c r="D87" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>19.4%</t>
+          <t>8.3%</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Rp1.600.000</t>
+          <t>Rp600.000</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
@@ -3300,14 +3300,14 @@
         </is>
       </c>
       <c r="C93" t="n">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="D93" t="n">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>10.8%</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3317,7 +3317,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Rp99.000</t>
+          <t>Rp50.000 - Rp99.000</t>
         </is>
       </c>
     </row>
@@ -3489,16 +3489,16 @@
         <v>68</v>
       </c>
       <c r="D99" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>20.6%</t>
+          <t>23.5%</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Rp2.046.000</t>
+          <t>Rp2.444.000</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
@@ -3819,16 +3819,16 @@
         <v>162</v>
       </c>
       <c r="D7" t="n">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>24.1%</t>
+          <t>25.3%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rp6.270.000</t>
+          <t>Rp6.620.000</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -4005,16 +4005,16 @@
         <v>50</v>
       </c>
       <c r="D13" t="n">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>24.0%</t>
+          <t>30.0%</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rp4.160.000</t>
+          <t>Rp4.880.000</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -4036,16 +4036,16 @@
         <v>70</v>
       </c>
       <c r="D14" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>28.6%</t>
+          <t>31.4%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp2.000.000</t>
+          <t>Rp2.200.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -4098,16 +4098,16 @@
         <v>105</v>
       </c>
       <c r="D16" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>28.6%</t>
+          <t>23.8%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp12.900.000</t>
+          <t>Rp10.650.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -4160,16 +4160,16 @@
         <v>54</v>
       </c>
       <c r="D18" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>37.0%</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rp4.050.000</t>
+          <t>Rp4.650.000</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -4191,16 +4191,16 @@
         <v>36</v>
       </c>
       <c r="D19" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>13.9%</t>
+          <t>19.4%</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rp625.000</t>
+          <t>Rp875.000</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -4253,16 +4253,16 @@
         <v>16</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rp2.492.000</t>
+          <t>Rp3.041.000</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -4343,14 +4343,14 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D24" t="n">
         <v>30</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>43.4%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -4749,16 +4749,16 @@
         <v>159</v>
       </c>
       <c r="D37" t="n">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>27.0%</t>
+          <t>27.7%</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rp16.200.000</t>
+          <t>Rp16.800.000</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -4780,16 +4780,16 @@
         <v>45</v>
       </c>
       <c r="D38" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>4.4%</t>
+          <t>8.9%</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rp550.000</t>
+          <t>Rp1.100.000</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -4904,16 +4904,16 @@
         <v>48</v>
       </c>
       <c r="D42" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>64.6%</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rp10.000.000</t>
+          <t>Rp9.750.000</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -5121,16 +5121,16 @@
         <v>80</v>
       </c>
       <c r="D49" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>26.2%</t>
+          <t>27.5%</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Rp3.825.000</t>
+          <t>Rp3.950.000</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -5307,16 +5307,16 @@
         <v>68</v>
       </c>
       <c r="D55" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>36.8%</t>
+          <t>38.2%</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Rp7.330.000</t>
+          <t>Rp7.660.000</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -5369,16 +5369,16 @@
         <v>75</v>
       </c>
       <c r="D57" t="n">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>6.7%</t>
+          <t>10.7%</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Rp337.000</t>
+          <t>Rp514.000</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -5586,16 +5586,16 @@
         <v>34</v>
       </c>
       <c r="D64" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>23.5%</t>
+          <t>29.4%</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Rp1.952.000</t>
+          <t>Rp2.330.000</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -5617,16 +5617,16 @@
         <v>90</v>
       </c>
       <c r="D65" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>34.4%</t>
+          <t>36.7%</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Rp10.750.000</t>
+          <t>Rp11.250.000</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -5648,16 +5648,16 @@
         <v>102</v>
       </c>
       <c r="D66" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>21.6%</t>
+          <t>22.5%</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Rp6.507.000</t>
+          <t>Rp6.804.000</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -5679,16 +5679,16 @@
         <v>234</v>
       </c>
       <c r="D67" t="n">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>17.5%</t>
+          <t>17.9%</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Rp4.868.000</t>
+          <t>Rp4.958.000</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -5741,16 +5741,16 @@
         <v>144</v>
       </c>
       <c r="D69" t="n">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>13.2%</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Rp8.200.000</t>
+          <t>Rp8.350.000</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -5834,16 +5834,16 @@
         <v>162</v>
       </c>
       <c r="D72" t="n">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>17.3%</t>
+          <t>18.5%</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Rp13.800.000</t>
+          <t>Rp14.500.000</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -6040,16 +6040,16 @@
         <v>102</v>
       </c>
       <c r="D5" t="n">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>19.6%</t>
+          <t>21.6%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp6.500.000</t>
+          <t>Rp7.200.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -6133,16 +6133,16 @@
         <v>256</v>
       </c>
       <c r="D8" t="n">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>24.2%</t>
+          <t>23.0%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rp30.100.000</t>
+          <t>Rp27.150.000</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -6164,16 +6164,16 @@
         <v>54</v>
       </c>
       <c r="D9" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>35.2%</t>
+          <t>37.0%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rp2.875.000</t>
+          <t>Rp3.050.000</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -6195,16 +6195,16 @@
         <v>42</v>
       </c>
       <c r="D10" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>57.1%</t>
+          <t>52.4%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp6.100.000</t>
+          <t>Rp5.800.000</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -6226,16 +6226,16 @@
         <v>72</v>
       </c>
       <c r="D11" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>30.6%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rp5.560.000</t>
+          <t>Rp5.920.000</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -6443,16 +6443,16 @@
         <v>34</v>
       </c>
       <c r="D18" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>32.4%</t>
+          <t>41.2%</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rp2.100.000</t>
+          <t>Rp2.650.000</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -6505,16 +6505,16 @@
         <v>15</v>
       </c>
       <c r="D20" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>26.7%</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rp684.000</t>
+          <t>Rp852.000</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -6618,16 +6618,16 @@
         <v>186</v>
       </c>
       <c r="D2" t="n">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>16.1%</t>
+          <t>15.6%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp9.360.000</t>
+          <t>Rp9.110.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -6649,16 +6649,16 @@
         <v>86</v>
       </c>
       <c r="D3" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>9.3%</t>
+          <t>10.5%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp6.100.000</t>
+          <t>Rp7.800.000</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -6680,16 +6680,16 @@
         <v>74</v>
       </c>
       <c r="D4" t="n">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>41.9%</t>
+          <t>45.9%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rp9.315.000</t>
+          <t>Rp9.990.000</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -6711,16 +6711,16 @@
         <v>90</v>
       </c>
       <c r="D5" t="n">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>4.4%</t>
+          <t>8.9%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp406.000</t>
+          <t>Rp842.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -6835,16 +6835,16 @@
         <v>85</v>
       </c>
       <c r="D9" t="n">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>36.5%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rp7.044.000</t>
+          <t>Rp7.469.000</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -6866,16 +6866,16 @@
         <v>60</v>
       </c>
       <c r="D10" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>23.3%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp3.000.000</t>
+          <t>Rp3.400.000</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -6897,16 +6897,16 @@
         <v>216</v>
       </c>
       <c r="D11" t="n">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>35.6%</t>
+          <t>34.7%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rp19.455.000</t>
+          <t>Rp19.225.000</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -7021,16 +7021,16 @@
         <v>96</v>
       </c>
       <c r="D15" t="n">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>6.2%</t>
+          <t>8.3%</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rp810.000</t>
+          <t>Rp1.080.000</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -7052,16 +7052,16 @@
         <v>108</v>
       </c>
       <c r="D16" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>32.4%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp6.350.000</t>
+          <t>Rp6.550.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -7145,16 +7145,16 @@
         <v>39</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>46.2%</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rp2.935.000</t>
+          <t>Rp4.149.000</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -7269,16 +7269,16 @@
         <v>126</v>
       </c>
       <c r="D23" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>34.1%</t>
+          <t>34.9%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp6.041.000</t>
+          <t>Rp6.216.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -7300,16 +7300,16 @@
         <v>90</v>
       </c>
       <c r="D24" t="n">
-        <v>64</v>
+        <v>47</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>28.9%</t>
+          <t>47.8%</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rp5.895.000</t>
+          <t>Rp9.075.000</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -7362,16 +7362,16 @@
         <v>108</v>
       </c>
       <c r="D26" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>29.6%</t>
+          <t>30.6%</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rp6.880.000</t>
+          <t>Rp7.130.000</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -7424,16 +7424,16 @@
         <v>96</v>
       </c>
       <c r="D28" t="n">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>18.8%</t>
+          <t>20.8%</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rp3.700.000</t>
+          <t>Rp4.200.000</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -7610,16 +7610,16 @@
         <v>108</v>
       </c>
       <c r="D34" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>47.2%</t>
+          <t>48.1%</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rp11.145.000</t>
+          <t>Rp11.340.000</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -7641,16 +7641,16 @@
         <v>187</v>
       </c>
       <c r="D35" t="n">
-        <v>113</v>
+        <v>96</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>39.6%</t>
+          <t>48.7%</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rp14.075.000</t>
+          <t>Rp15.525.000</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -7703,16 +7703,16 @@
         <v>84</v>
       </c>
       <c r="D37" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>17.9%</t>
+          <t>15.5%</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rp3.623.000</t>
+          <t>Rp3.053.000</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -7734,16 +7734,16 @@
         <v>170</v>
       </c>
       <c r="D38" t="n">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>18.2%</t>
+          <t>21.8%</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rp4.150.000</t>
+          <t>Rp4.750.000</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -7827,16 +7827,16 @@
         <v>150</v>
       </c>
       <c r="D41" t="n">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>54.0%</t>
+          <t>56.0%</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rp25.050.000</t>
+          <t>Rp26.010.000</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -7982,16 +7982,16 @@
         <v>174</v>
       </c>
       <c r="D46" t="n">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>36.2%</t>
+          <t>39.1%</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Rp26.650.000</t>
+          <t>Rp29.650.000</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -8137,16 +8137,16 @@
         <v>98</v>
       </c>
       <c r="D51" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>24.5%</t>
+          <t>23.5%</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Rp5.310.000</t>
+          <t>Rp5.160.000</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -8168,16 +8168,16 @@
         <v>144</v>
       </c>
       <c r="D52" t="n">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>29.9%</t>
+          <t>30.6%</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Rp7.175.000</t>
+          <t>Rp7.350.000</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -8199,16 +8199,16 @@
         <v>90</v>
       </c>
       <c r="D53" t="n">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>14.4%</t>
+          <t>30.0%</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Rp3.100.000</t>
+          <t>Rp6.500.000</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -8467,16 +8467,16 @@
         <v>51</v>
       </c>
       <c r="D8" t="n">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>17.6%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rp1.040.000</t>
+          <t>Rp1.490.000</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -8560,16 +8560,16 @@
         <v>72</v>
       </c>
       <c r="D11" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>43.1%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rp7.510.000</t>
+          <t>Rp7.710.000</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -8622,16 +8622,16 @@
         <v>51</v>
       </c>
       <c r="D13" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>41.2%</t>
+          <t>45.1%</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rp3.224.992</t>
+          <t>Rp3.474.992</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -8653,16 +8653,16 @@
         <v>72</v>
       </c>
       <c r="D14" t="n">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>9.7%</t>
+          <t>19.4%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp875.000</t>
+          <t>Rp2.125.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -8715,16 +8715,16 @@
         <v>54</v>
       </c>
       <c r="D16" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>29.6%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp3.535.000</t>
+          <t>Rp4.035.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -8808,16 +8808,16 @@
         <v>102</v>
       </c>
       <c r="D19" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>68.6%</t>
+          <t>65.7%</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rp26.080.000</t>
+          <t>Rp24.820.000</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8901,16 +8901,16 @@
         <v>144</v>
       </c>
       <c r="D22" t="n">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>13.9%</t>
+          <t>15.3%</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rp3.840.000</t>
+          <t>Rp4.230.000</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -8932,16 +8932,16 @@
         <v>36</v>
       </c>
       <c r="D23" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>30.6%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp1.891.000</t>
+          <t>Rp1.756.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -9397,16 +9397,16 @@
         <v>64</v>
       </c>
       <c r="D38" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>7.8%</t>
+          <t>9.4%</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rp713.000</t>
+          <t>Rp838.000</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">

--- a/laporan_padel_dki_jakarta_2026-10-28.xlsx
+++ b/laporan_padel_dki_jakarta_2026-10-28.xlsx
@@ -544,16 +544,16 @@
         <v>144</v>
       </c>
       <c r="D4" t="n">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>18.8%</t>
+          <t>19.4%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rp12.460.000</t>
+          <t>Rp12.760.000</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -699,16 +699,16 @@
         <v>68</v>
       </c>
       <c r="D9" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>41.2%</t>
+          <t>42.6%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rp2.772.000</t>
+          <t>Rp2.871.000</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -730,16 +730,16 @@
         <v>72</v>
       </c>
       <c r="D10" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>26.4%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp5.678.985</t>
+          <t>Rp6.027.984</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -761,16 +761,16 @@
         <v>126</v>
       </c>
       <c r="D11" t="n">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>9.5%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rp3.375.000</t>
+          <t>Rp3.875.000</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -823,16 +823,16 @@
         <v>68</v>
       </c>
       <c r="D13" t="n">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>5.9%</t>
+          <t>11.8%</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rp900.000</t>
+          <t>Rp1.700.000</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -854,16 +854,16 @@
         <v>162</v>
       </c>
       <c r="D14" t="n">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>21.6%</t>
+          <t>21.0%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp8.550.000</t>
+          <t>Rp8.422.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -885,16 +885,16 @@
         <v>90</v>
       </c>
       <c r="D15" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>30.0%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rp6.525.000</t>
+          <t>Rp6.100.000</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -978,16 +978,16 @@
         <v>162</v>
       </c>
       <c r="D18" t="n">
-        <v>156</v>
+        <v>147</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>3.7%</t>
+          <t>9.3%</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rp700.000</t>
+          <t>Rp2.500.000</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1102,16 +1102,16 @@
         <v>136</v>
       </c>
       <c r="D22" t="n">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>26.5%</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rp11.346.000</t>
+          <t>Rp11.844.000</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1133,16 +1133,16 @@
         <v>102</v>
       </c>
       <c r="D23" t="n">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>26.5%</t>
+          <t>28.4%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp5.000.000</t>
+          <t>Rp5.300.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1195,16 +1195,16 @@
         <v>64</v>
       </c>
       <c r="D25" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>20.3%</t>
+          <t>23.4%</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rp2.850.000</t>
+          <t>Rp3.350.000</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1226,16 +1226,16 @@
         <v>68</v>
       </c>
       <c r="D26" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>7.4%</t>
+          <t>8.8%</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rp925.000</t>
+          <t>Rp1.125.000</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1288,16 +1288,16 @@
         <v>36</v>
       </c>
       <c r="D28" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rp1.292.000</t>
+          <t>Rp1.491.000</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -1381,16 +1381,16 @@
         <v>102</v>
       </c>
       <c r="D31" t="n">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>19.6%</t>
+          <t>22.5%</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rp1.981.000</t>
+          <t>Rp2.278.000</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -1443,16 +1443,16 @@
         <v>85</v>
       </c>
       <c r="D33" t="n">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>22.4%</t>
+          <t>15.3%</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rp2.977.000</t>
+          <t>Rp1.787.000</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -1474,16 +1474,16 @@
         <v>68</v>
       </c>
       <c r="D34" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>27.9%</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rp3.105.000</t>
+          <t>Rp3.565.000</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -1567,16 +1567,16 @@
         <v>72</v>
       </c>
       <c r="D37" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>45.8%</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rp4.975.000</t>
+          <t>Rp5.165.000</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -1691,16 +1691,16 @@
         <v>54</v>
       </c>
       <c r="D41" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rp1.170.000</t>
+          <t>Rp1.755.000</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -1722,16 +1722,16 @@
         <v>51</v>
       </c>
       <c r="D42" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>41.2%</t>
+          <t>45.1%</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rp2.175.000</t>
+          <t>Rp2.515.000</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -1815,16 +1815,16 @@
         <v>198</v>
       </c>
       <c r="D45" t="n">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>9.6%</t>
+          <t>11.6%</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rp2.700.000</t>
+          <t>Rp3.300.000</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -1846,16 +1846,16 @@
         <v>60</v>
       </c>
       <c r="D46" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>18.3%</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Rp2.520.000</t>
+          <t>Rp2.310.000</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -1877,16 +1877,16 @@
         <v>42</v>
       </c>
       <c r="D47" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>23.8%</t>
+          <t>26.2%</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Rp1.800.000</t>
+          <t>Rp1.875.000</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -1939,16 +1939,16 @@
         <v>105</v>
       </c>
       <c r="D49" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>29.5%</t>
+          <t>30.5%</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Rp6.050.000</t>
+          <t>Rp6.300.000</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -2001,16 +2001,16 @@
         <v>56</v>
       </c>
       <c r="D51" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>8.9%</t>
+          <t>10.7%</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Rp2.750.000</t>
+          <t>Rp3.300.000</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -2094,16 +2094,16 @@
         <v>60</v>
       </c>
       <c r="D54" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>1.7%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Rp96.000</t>
+          <t>Rp204.000</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -2156,16 +2156,16 @@
         <v>17</v>
       </c>
       <c r="D56" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>23.5%</t>
+          <t>29.4%</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Rp698.000</t>
+          <t>Rp847.000</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -2187,16 +2187,16 @@
         <v>48</v>
       </c>
       <c r="D57" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Rp960.000</t>
+          <t>Rp1.680.000</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -2249,16 +2249,16 @@
         <v>32</v>
       </c>
       <c r="D59" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>31.2%</t>
+          <t>40.6%</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Rp2.300.000</t>
+          <t>Rp3.125.000</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -2373,16 +2373,16 @@
         <v>72</v>
       </c>
       <c r="D63" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Rp2.560.000</t>
+          <t>Rp2.720.000</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -2497,16 +2497,16 @@
         <v>90</v>
       </c>
       <c r="D67" t="n">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>28.9%</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Rp4.524.000</t>
+          <t>Rp7.716.000</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -2528,16 +2528,16 @@
         <v>41</v>
       </c>
       <c r="D68" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>2.4%</t>
+          <t>12.2%</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Rp230.000</t>
+          <t>Rp1.150.000</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -2590,16 +2590,16 @@
         <v>176</v>
       </c>
       <c r="D70" t="n">
-        <v>161</v>
+        <v>151</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>8.5%</t>
+          <t>14.2%</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Rp3.486.000</t>
+          <t>Rp6.076.000</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -2683,16 +2683,16 @@
         <v>72</v>
       </c>
       <c r="D73" t="n">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>9.7%</t>
+          <t>15.3%</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Rp810.000</t>
+          <t>Rp1.490.000</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -2714,16 +2714,16 @@
         <v>90</v>
       </c>
       <c r="D74" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>17.8%</t>
+          <t>18.9%</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Rp4.700.000</t>
+          <t>Rp5.025.000</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -2745,16 +2745,16 @@
         <v>96</v>
       </c>
       <c r="D75" t="n">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>10.4%</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Rp2.620.000</t>
+          <t>Rp2.100.000</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -2838,16 +2838,16 @@
         <v>128</v>
       </c>
       <c r="D78" t="n">
-        <v>113</v>
+        <v>122</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>11.7%</t>
+          <t>4.7%</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Rp3.575.000</t>
+          <t>Rp1.370.000</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -2869,16 +2869,16 @@
         <v>108</v>
       </c>
       <c r="D79" t="n">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>17.6%</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Rp2.225.000</t>
+          <t>Rp2.325.000</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -2931,16 +2931,16 @@
         <v>126</v>
       </c>
       <c r="D81" t="n">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>25.4%</t>
+          <t>30.2%</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Rp4.368.000</t>
+          <t>Rp5.562.000</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -3055,16 +3055,16 @@
         <v>135</v>
       </c>
       <c r="D85" t="n">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>13.3%</t>
+          <t>14.1%</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Rp3.750.000</t>
+          <t>Rp4.030.000</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -3117,16 +3117,16 @@
         <v>36</v>
       </c>
       <c r="D87" t="n">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>8.3%</t>
+          <t>19.4%</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Rp600.000</t>
+          <t>Rp1.600.000</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
@@ -3179,16 +3179,16 @@
         <v>138</v>
       </c>
       <c r="D89" t="n">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>13.8%</t>
+          <t>15.2%</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Rp4.000.000</t>
+          <t>Rp4.450.000</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
@@ -3303,16 +3303,16 @@
         <v>37</v>
       </c>
       <c r="D93" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>10.8%</t>
+          <t>13.5%</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Rp396.000</t>
+          <t>Rp495.000</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
@@ -3365,16 +3365,16 @@
         <v>34</v>
       </c>
       <c r="D95" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>35.3%</t>
+          <t>29.4%</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Rp2.300.000</t>
+          <t>Rp1.850.000</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
@@ -3427,16 +3427,16 @@
         <v>112</v>
       </c>
       <c r="D97" t="n">
-        <v>104</v>
+        <v>96</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>7.1%</t>
+          <t>14.3%</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Rp1.520.000</t>
+          <t>Rp3.280.000</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
@@ -3458,16 +3458,16 @@
         <v>112</v>
       </c>
       <c r="D98" t="n">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>26.8%</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Rp3.995.000</t>
+          <t>Rp4.395.000</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
@@ -3582,16 +3582,16 @@
         <v>36</v>
       </c>
       <c r="D102" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Rp1.200.000</t>
+          <t>Rp1.500.000</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
@@ -3726,16 +3726,16 @@
         <v>102</v>
       </c>
       <c r="D4" t="n">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2.0%</t>
+          <t>7.8%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rp700.000</t>
+          <t>Rp3.034.000</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -3757,16 +3757,16 @@
         <v>96</v>
       </c>
       <c r="D5" t="n">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>18.8%</t>
+          <t>21.9%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp5.100.000</t>
+          <t>Rp6.150.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -3912,16 +3912,16 @@
         <v>144</v>
       </c>
       <c r="D10" t="n">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>9.0%</t>
+          <t>10.4%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp2.123.000</t>
+          <t>Rp2.823.000</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4036,16 +4036,16 @@
         <v>70</v>
       </c>
       <c r="D14" t="n">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>31.4%</t>
+          <t>22.9%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp2.200.000</t>
+          <t>Rp1.600.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -4129,16 +4129,16 @@
         <v>65</v>
       </c>
       <c r="D17" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>10.8%</t>
+          <t>16.9%</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rp2.835.000</t>
+          <t>Rp4.455.000</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -4160,16 +4160,16 @@
         <v>54</v>
       </c>
       <c r="D18" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>37.0%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rp4.650.000</t>
+          <t>Rp5.850.000</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -4191,16 +4191,16 @@
         <v>36</v>
       </c>
       <c r="D19" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>19.4%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rp875.000</t>
+          <t>Rp1.000.000</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -4470,16 +4470,16 @@
         <v>170</v>
       </c>
       <c r="D28" t="n">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>28.8%</t>
+          <t>30.0%</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rp13.925.000</t>
+          <t>Rp14.425.000</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -4625,16 +4625,16 @@
         <v>90</v>
       </c>
       <c r="D33" t="n">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>32.2%</t>
+          <t>23.3%</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rp6.325.000</t>
+          <t>Rp4.525.000</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -4749,16 +4749,16 @@
         <v>159</v>
       </c>
       <c r="D37" t="n">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>27.7%</t>
+          <t>27.0%</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rp16.800.000</t>
+          <t>Rp16.400.000</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -4935,16 +4935,16 @@
         <v>64</v>
       </c>
       <c r="D43" t="n">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>17.2%</t>
+          <t>23.4%</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rp2.200.000</t>
+          <t>Rp3.000.000</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -5121,16 +5121,16 @@
         <v>80</v>
       </c>
       <c r="D49" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>27.5%</t>
+          <t>28.7%</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Rp3.950.000</t>
+          <t>Rp4.175.000</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -5183,16 +5183,16 @@
         <v>72</v>
       </c>
       <c r="D51" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>31.9%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Rp9.012.000</t>
+          <t>Rp9.408.000</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -5307,16 +5307,16 @@
         <v>68</v>
       </c>
       <c r="D55" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>38.2%</t>
+          <t>39.7%</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Rp7.660.000</t>
+          <t>Rp7.935.000</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -5369,16 +5369,16 @@
         <v>75</v>
       </c>
       <c r="D57" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>10.7%</t>
+          <t>12.0%</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Rp514.000</t>
+          <t>Rp576.000</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -5400,16 +5400,16 @@
         <v>51</v>
       </c>
       <c r="D58" t="n">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>13.7%</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Rp300.000</t>
+          <t>Rp1.175.000</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -5617,16 +5617,16 @@
         <v>90</v>
       </c>
       <c r="D65" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>36.7%</t>
+          <t>34.4%</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Rp11.250.000</t>
+          <t>Rp10.450.000</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -5679,16 +5679,16 @@
         <v>234</v>
       </c>
       <c r="D67" t="n">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>17.9%</t>
+          <t>19.2%</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Rp4.958.000</t>
+          <t>Rp5.288.000</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -5865,16 +5865,16 @@
         <v>90</v>
       </c>
       <c r="D73" t="n">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>13.3%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Rp4.200.000</t>
+          <t>Rp5.350.000</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -6009,16 +6009,16 @@
         <v>30</v>
       </c>
       <c r="D4" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>46.7%</t>
+          <t>53.3%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rp1.825.000</t>
+          <t>Rp2.325.000</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -6040,16 +6040,16 @@
         <v>102</v>
       </c>
       <c r="D5" t="n">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>21.6%</t>
+          <t>24.5%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp7.200.000</t>
+          <t>Rp8.250.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -6133,16 +6133,16 @@
         <v>256</v>
       </c>
       <c r="D8" t="n">
-        <v>197</v>
+        <v>207</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>23.0%</t>
+          <t>19.1%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rp27.150.000</t>
+          <t>Rp20.400.000</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -6288,16 +6288,16 @@
         <v>68</v>
       </c>
       <c r="D13" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>30.9%</t>
+          <t>32.4%</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rp7.035.000</t>
+          <t>Rp7.370.000</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -6545,7 +6545,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rp2.994.000</t>
+          <t>Rp3.994.000</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -6618,16 +6618,16 @@
         <v>186</v>
       </c>
       <c r="D2" t="n">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>15.6%</t>
+          <t>17.7%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp9.110.000</t>
+          <t>Rp9.430.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -6680,16 +6680,16 @@
         <v>74</v>
       </c>
       <c r="D4" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>45.9%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rp9.990.000</t>
+          <t>Rp10.590.000</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -6711,16 +6711,16 @@
         <v>90</v>
       </c>
       <c r="D5" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>8.9%</t>
+          <t>10.0%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp842.000</t>
+          <t>Rp911.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -6742,16 +6742,16 @@
         <v>216</v>
       </c>
       <c r="D6" t="n">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>23.6%</t>
+          <t>24.5%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rp10.935.000</t>
+          <t>Rp11.325.000</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -6835,16 +6835,16 @@
         <v>85</v>
       </c>
       <c r="D9" t="n">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>43.5%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rp7.469.000</t>
+          <t>Rp8.255.000</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -7021,16 +7021,16 @@
         <v>96</v>
       </c>
       <c r="D15" t="n">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>8.3%</t>
+          <t>9.4%</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rp1.080.000</t>
+          <t>Rp1.380.000</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -7176,16 +7176,16 @@
         <v>90</v>
       </c>
       <c r="D20" t="n">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>13.3%</t>
+          <t>15.6%</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rp1.188.000</t>
+          <t>Rp1.386.000</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -7207,16 +7207,16 @@
         <v>153</v>
       </c>
       <c r="D21" t="n">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>47.7%</t>
+          <t>50.3%</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rp23.400.000</t>
+          <t>Rp24.400.000</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -7238,16 +7238,16 @@
         <v>72</v>
       </c>
       <c r="D22" t="n">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>29.2%</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rp8.175.000</t>
+          <t>Rp6.075.000</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -7269,16 +7269,16 @@
         <v>126</v>
       </c>
       <c r="D23" t="n">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>34.9%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp6.216.000</t>
+          <t>Rp5.866.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -7300,16 +7300,16 @@
         <v>90</v>
       </c>
       <c r="D24" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>47.8%</t>
+          <t>46.7%</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rp9.075.000</t>
+          <t>Rp8.820.000</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -7331,16 +7331,16 @@
         <v>48</v>
       </c>
       <c r="D25" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>10.4%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rp739.000</t>
+          <t>Rp999.000</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -7424,16 +7424,16 @@
         <v>96</v>
       </c>
       <c r="D28" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>20.8%</t>
+          <t>21.9%</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rp4.200.000</t>
+          <t>Rp4.450.000</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -7455,16 +7455,16 @@
         <v>64</v>
       </c>
       <c r="D29" t="n">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>3.1%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rp350.000</t>
+          <t>Rp2.000.000</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -7486,16 +7486,16 @@
         <v>84</v>
       </c>
       <c r="D30" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>17.9%</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rp5.950.000</t>
+          <t>Rp6.650.000</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -7517,16 +7517,16 @@
         <v>96</v>
       </c>
       <c r="D31" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>26.0%</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rp3.708.000</t>
+          <t>Rp3.958.000</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -7610,16 +7610,16 @@
         <v>108</v>
       </c>
       <c r="D34" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>48.1%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rp11.340.000</t>
+          <t>Rp11.830.000</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -7641,16 +7641,16 @@
         <v>187</v>
       </c>
       <c r="D35" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>48.7%</t>
+          <t>48.1%</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rp15.525.000</t>
+          <t>Rp15.475.000</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -7703,16 +7703,16 @@
         <v>84</v>
       </c>
       <c r="D37" t="n">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>15.5%</t>
+          <t>17.9%</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rp3.053.000</t>
+          <t>Rp3.623.000</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -7734,16 +7734,16 @@
         <v>170</v>
       </c>
       <c r="D38" t="n">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>21.8%</t>
+          <t>22.9%</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rp4.750.000</t>
+          <t>Rp5.000.000</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -7827,16 +7827,16 @@
         <v>150</v>
       </c>
       <c r="D41" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>56.0%</t>
+          <t>57.3%</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rp26.010.000</t>
+          <t>Rp26.710.000</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -7858,16 +7858,16 @@
         <v>120</v>
       </c>
       <c r="D42" t="n">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>5.8%</t>
+          <t>9.2%</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rp3.397.000</t>
+          <t>Rp4.997.000</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -7889,16 +7889,16 @@
         <v>80</v>
       </c>
       <c r="D43" t="n">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>15.0%</t>
+          <t>18.8%</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rp2.700.000</t>
+          <t>Rp3.375.000</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -7982,16 +7982,16 @@
         <v>174</v>
       </c>
       <c r="D46" t="n">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>39.1%</t>
+          <t>39.7%</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Rp29.650.000</t>
+          <t>Rp30.250.000</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -8168,16 +8168,16 @@
         <v>144</v>
       </c>
       <c r="D52" t="n">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>30.6%</t>
+          <t>31.9%</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Rp7.350.000</t>
+          <t>Rp7.675.000</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -8199,16 +8199,16 @@
         <v>90</v>
       </c>
       <c r="D53" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>30.0%</t>
+          <t>26.7%</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Rp6.500.000</t>
+          <t>Rp5.600.000</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -8281,16 +8281,16 @@
         <v>72</v>
       </c>
       <c r="D2" t="n">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>8.3%</t>
+          <t>13.9%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp750.000</t>
+          <t>Rp1.250.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -8312,16 +8312,16 @@
         <v>136</v>
       </c>
       <c r="D3" t="n">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>32.4%</t>
+          <t>33.8%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp8.055.000</t>
+          <t>Rp8.315.000</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -8343,16 +8343,16 @@
         <v>34</v>
       </c>
       <c r="D4" t="n">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>8.8%</t>
+          <t>17.6%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rp780.000</t>
+          <t>Rp1.560.000</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -8374,16 +8374,16 @@
         <v>86</v>
       </c>
       <c r="D5" t="n">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>30.2%</t>
+          <t>34.9%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp7.500.000</t>
+          <t>Rp8.900.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -8405,16 +8405,16 @@
         <v>72</v>
       </c>
       <c r="D6" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>20.8%</t>
+          <t>18.1%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rp4.061.000</t>
+          <t>Rp3.463.000</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -8622,16 +8622,16 @@
         <v>51</v>
       </c>
       <c r="D13" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>45.1%</t>
+          <t>51.0%</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rp3.474.992</t>
+          <t>Rp3.999.990</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -8653,16 +8653,16 @@
         <v>72</v>
       </c>
       <c r="D14" t="n">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>19.4%</t>
+          <t>23.6%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp2.125.000</t>
+          <t>Rp2.725.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -8715,16 +8715,16 @@
         <v>54</v>
       </c>
       <c r="D16" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>37.0%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp4.035.000</t>
+          <t>Rp4.615.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -8746,16 +8746,16 @@
         <v>54</v>
       </c>
       <c r="D17" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>27.8%</t>
+          <t>29.6%</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rp2.400.000</t>
+          <t>Rp2.560.000</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -8777,16 +8777,16 @@
         <v>48</v>
       </c>
       <c r="D18" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>31.2%</t>
+          <t>35.4%</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rp3.525.000</t>
+          <t>Rp4.175.000</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -8808,16 +8808,16 @@
         <v>102</v>
       </c>
       <c r="D19" t="n">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>65.7%</t>
+          <t>69.6%</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rp24.820.000</t>
+          <t>Rp26.560.000</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8839,16 +8839,16 @@
         <v>17</v>
       </c>
       <c r="D20" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>5.9%</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp160.000</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8870,16 +8870,16 @@
         <v>68</v>
       </c>
       <c r="D21" t="n">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>4.4%</t>
+          <t>8.8%</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rp945.000</t>
+          <t>Rp1.890.000</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -8901,16 +8901,16 @@
         <v>144</v>
       </c>
       <c r="D22" t="n">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>15.3%</t>
+          <t>17.4%</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rp4.230.000</t>
+          <t>Rp4.815.000</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -8932,16 +8932,16 @@
         <v>36</v>
       </c>
       <c r="D23" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>30.6%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp1.756.000</t>
+          <t>Rp1.955.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -9025,16 +9025,16 @@
         <v>54</v>
       </c>
       <c r="D26" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rp4.050.000</t>
+          <t>Rp4.500.000</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -9087,16 +9087,16 @@
         <v>36</v>
       </c>
       <c r="D28" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>36.1%</t>
+          <t>47.2%</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rp2.550.000</t>
+          <t>Rp3.550.000</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -9180,16 +9180,16 @@
         <v>54</v>
       </c>
       <c r="D31" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>20.4%</t>
+          <t>24.1%</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rp2.642.000</t>
+          <t>Rp3.206.000</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -9242,16 +9242,16 @@
         <v>36</v>
       </c>
       <c r="D33" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rp1.580.000</t>
+          <t>Rp1.755.000</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -9304,16 +9304,16 @@
         <v>51</v>
       </c>
       <c r="D35" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>9.8%</t>
+          <t>5.9%</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rp925.000</t>
+          <t>Rp555.000</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -9335,16 +9335,16 @@
         <v>72</v>
       </c>
       <c r="D36" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>30.6%</t>
+          <t>31.9%</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rp2.080.000</t>
+          <t>Rp2.179.000</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -9397,16 +9397,16 @@
         <v>64</v>
       </c>
       <c r="D38" t="n">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>9.4%</t>
+          <t>14.1%</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rp838.000</t>
+          <t>Rp1.345.000</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -9428,16 +9428,16 @@
         <v>90</v>
       </c>
       <c r="D39" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>13.3%</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rp2.275.000</t>
+          <t>Rp2.775.000</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">

--- a/laporan_padel_dki_jakarta_2026-10-28.xlsx
+++ b/laporan_padel_dki_jakarta_2026-10-28.xlsx
@@ -699,16 +699,16 @@
         <v>68</v>
       </c>
       <c r="D9" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>42.6%</t>
+          <t>44.1%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rp2.871.000</t>
+          <t>Rp2.970.000</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -730,16 +730,16 @@
         <v>72</v>
       </c>
       <c r="D10" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>26.4%</t>
+          <t>29.2%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp6.027.984</t>
+          <t>Rp6.323.984</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -854,16 +854,16 @@
         <v>162</v>
       </c>
       <c r="D14" t="n">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>21.0%</t>
+          <t>24.1%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp8.422.000</t>
+          <t>Rp9.602.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -978,16 +978,16 @@
         <v>162</v>
       </c>
       <c r="D18" t="n">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>9.3%</t>
+          <t>9.9%</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rp2.500.000</t>
+          <t>Rp2.600.000</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1009,16 +1009,16 @@
         <v>108</v>
       </c>
       <c r="D19" t="n">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>23.1%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rp4.580.000</t>
+          <t>Rp4.780.000</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1288,16 +1288,16 @@
         <v>36</v>
       </c>
       <c r="D28" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rp1.491.000</t>
+          <t>Rp1.590.000</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -1722,16 +1722,16 @@
         <v>51</v>
       </c>
       <c r="D42" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>45.1%</t>
+          <t>39.2%</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rp2.515.000</t>
+          <t>Rp2.260.000</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -1753,16 +1753,16 @@
         <v>234</v>
       </c>
       <c r="D43" t="n">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>8.5%</t>
+          <t>9.0%</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rp4.792.000</t>
+          <t>Rp4.991.000</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -1784,16 +1784,16 @@
         <v>72</v>
       </c>
       <c r="D44" t="n">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rp9.380.000</t>
+          <t>Rp8.280.000</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -1815,16 +1815,16 @@
         <v>198</v>
       </c>
       <c r="D45" t="n">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>11.6%</t>
+          <t>12.6%</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rp3.300.000</t>
+          <t>Rp3.600.000</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -2125,16 +2125,16 @@
         <v>36</v>
       </c>
       <c r="D55" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp175.000</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -2869,16 +2869,16 @@
         <v>108</v>
       </c>
       <c r="D79" t="n">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>17.6%</t>
+          <t>18.5%</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Rp2.325.000</t>
+          <t>Rp2.400.000</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -2931,16 +2931,16 @@
         <v>126</v>
       </c>
       <c r="D81" t="n">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>30.2%</t>
+          <t>34.9%</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Rp5.562.000</t>
+          <t>Rp6.156.000</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -3241,16 +3241,16 @@
         <v>119</v>
       </c>
       <c r="D91" t="n">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>19.3%</t>
+          <t>20.2%</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Rp3.400.000</t>
+          <t>Rp3.580.000</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
@@ -3458,16 +3458,16 @@
         <v>112</v>
       </c>
       <c r="D98" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>26.8%</t>
+          <t>27.7%</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Rp4.395.000</t>
+          <t>Rp4.645.000</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
@@ -3695,16 +3695,16 @@
         <v>119</v>
       </c>
       <c r="D3" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>45.4%</t>
+          <t>46.2%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp13.429.500</t>
+          <t>Rp13.817.000</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -3726,16 +3726,16 @@
         <v>102</v>
       </c>
       <c r="D4" t="n">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>7.8%</t>
+          <t>9.8%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rp3.034.000</t>
+          <t>Rp3.812.000</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -3912,16 +3912,16 @@
         <v>144</v>
       </c>
       <c r="D10" t="n">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>10.4%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp2.823.000</t>
+          <t>Rp2.948.000</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4160,16 +4160,16 @@
         <v>54</v>
       </c>
       <c r="D18" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>48.1%</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rp5.850.000</t>
+          <t>Rp6.250.000</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -4842,16 +4842,16 @@
         <v>54</v>
       </c>
       <c r="D40" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>9.3%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rp925.000</t>
+          <t>Rp1.110.000</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -4966,16 +4966,16 @@
         <v>77</v>
       </c>
       <c r="D44" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>36.4%</t>
+          <t>35.1%</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rp10.200.000</t>
+          <t>Rp9.950.000</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -5978,16 +5978,16 @@
         <v>324</v>
       </c>
       <c r="D3" t="n">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>43.8%</t>
+          <t>42.0%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp28.902.500</t>
+          <t>Rp27.747.500</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -6040,16 +6040,16 @@
         <v>102</v>
       </c>
       <c r="D5" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>24.5%</t>
+          <t>25.5%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp8.250.000</t>
+          <t>Rp8.500.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -6257,16 +6257,16 @@
         <v>36</v>
       </c>
       <c r="D12" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>27.8%</t>
+          <t>30.6%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rp2.350.000</t>
+          <t>Rp2.469.000</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -6618,16 +6618,16 @@
         <v>186</v>
       </c>
       <c r="D2" t="n">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>17.7%</t>
+          <t>18.8%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp9.430.000</t>
+          <t>Rp10.330.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -6649,16 +6649,16 @@
         <v>86</v>
       </c>
       <c r="D3" t="n">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>10.5%</t>
+          <t>8.1%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp7.800.000</t>
+          <t>Rp7.300.000</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -6711,16 +6711,16 @@
         <v>90</v>
       </c>
       <c r="D5" t="n">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>10.0%</t>
+          <t>12.2%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp911.000</t>
+          <t>Rp1.049.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -6773,16 +6773,16 @@
         <v>144</v>
       </c>
       <c r="D7" t="n">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>18.1%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rp7.950.000</t>
+          <t>Rp8.300.000</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -7269,16 +7269,16 @@
         <v>126</v>
       </c>
       <c r="D23" t="n">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>34.9%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp5.866.000</t>
+          <t>Rp6.028.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -7641,16 +7641,16 @@
         <v>187</v>
       </c>
       <c r="D35" t="n">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>48.1%</t>
+          <t>50.8%</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rp15.475.000</t>
+          <t>Rp15.800.000</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -8106,16 +8106,16 @@
         <v>102</v>
       </c>
       <c r="D50" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>32.4%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Rp9.957.000</t>
+          <t>Rp10.186.000</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -8560,16 +8560,16 @@
         <v>72</v>
       </c>
       <c r="D11" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>43.1%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rp7.710.000</t>
+          <t>Rp7.495.000</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -8653,16 +8653,16 @@
         <v>72</v>
       </c>
       <c r="D14" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>23.6%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp2.725.000</t>
+          <t>Rp2.825.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
